--- a/evaluations/count/population_counting_results_final_NEW.xlsx
+++ b/evaluations/count/population_counting_results_final_NEW.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y59"/>
+  <dimension ref="A1:Y62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,33 +657,37 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G3" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H3" t="n">
-        <v>534</v>
+        <v>1453</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>426</v>
+        <v>965</v>
       </c>
       <c r="K3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N3" t="n">
         <v>256</v>
       </c>
@@ -702,19 +706,23 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>484.09</v>
+        <v>193.99</v>
       </c>
       <c r="T3" t="n">
-        <v>61.23</v>
+        <v>60.13</v>
       </c>
       <c r="U3" t="n">
-        <v>4.84</v>
+        <v>3.01</v>
       </c>
       <c r="V3" t="n">
         <v>237</v>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3</v>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -736,37 +744,33 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E4" t="n">
         <v>200</v>
       </c>
       <c r="F4" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G4" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H4" t="n">
-        <v>3117</v>
+        <v>930</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1841</v>
+        <v>735</v>
       </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>256</v>
       </c>
@@ -785,23 +789,19 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>105.69</v>
+        <v>463.41</v>
       </c>
       <c r="T4" t="n">
-        <v>37</v>
+        <v>52.13</v>
       </c>
       <c r="U4" t="n">
-        <v>5.71</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>237</v>
       </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3</v>
-      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -823,33 +823,37 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="G5" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>152</v>
+        <v>585</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>125</v>
+        <v>476</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N5" t="n">
         <v>256</v>
       </c>
@@ -868,19 +872,23 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>592.8200000000001</v>
+        <v>471.41</v>
       </c>
       <c r="T5" t="n">
-        <v>100.66</v>
+        <v>59.66</v>
       </c>
       <c r="U5" t="n">
-        <v>1.77</v>
+        <v>6.05</v>
       </c>
       <c r="V5" t="n">
         <v>237</v>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -902,37 +910,33 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" t="n">
-        <v>200</v>
-      </c>
       <c r="F6" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="G6" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="H6" t="n">
-        <v>950</v>
+        <v>1932</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>704</v>
+        <v>1352</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
         <v>256</v>
       </c>
@@ -951,23 +955,19 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>360.81</v>
+        <v>112.28</v>
       </c>
       <c r="T6" t="n">
-        <v>30.94</v>
+        <v>42.86</v>
       </c>
       <c r="U6" t="n">
-        <v>11.69</v>
+        <v>3.86</v>
       </c>
       <c r="V6" t="n">
         <v>237</v>
       </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3</v>
-      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -989,33 +989,37 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E7" t="n">
         <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G7" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>267</v>
+        <v>578</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>222</v>
+        <v>452</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N7" t="n">
         <v>256</v>
       </c>
@@ -1034,19 +1038,23 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>590.0700000000001</v>
+        <v>622.45</v>
       </c>
       <c r="T7" t="n">
-        <v>68.59</v>
+        <v>52.46</v>
       </c>
       <c r="U7" t="n">
-        <v>3.12</v>
+        <v>4.87</v>
       </c>
       <c r="V7" t="n">
         <v>237</v>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -1071,30 +1079,34 @@
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F8" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="G8" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>952</v>
+        <v>3453</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>604</v>
+        <v>2258</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N8" t="n">
         <v>256</v>
       </c>
@@ -1113,19 +1125,23 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>121.82</v>
+        <v>128.36</v>
       </c>
       <c r="T8" t="n">
-        <v>46.42</v>
+        <v>51.37</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>5.83</v>
       </c>
       <c r="V8" t="n">
         <v>237</v>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -1147,25 +1163,25 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="n">
         <v>100</v>
       </c>
-      <c r="E9" t="n">
-        <v>200</v>
-      </c>
       <c r="F9" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="G9" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="H9" t="n">
-        <v>969</v>
+        <v>239</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>775</v>
+        <v>198</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1192,13 +1208,13 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>392.56</v>
+        <v>626.4</v>
       </c>
       <c r="T9" t="n">
-        <v>48.76</v>
+        <v>116.4</v>
       </c>
       <c r="U9" t="n">
-        <v>12.04</v>
+        <v>3.26</v>
       </c>
       <c r="V9" t="n">
         <v>237</v>
@@ -1226,28 +1242,28 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" t="n">
         <v>50</v>
       </c>
-      <c r="E10" t="n">
-        <v>100</v>
-      </c>
       <c r="F10" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G10" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>1795</v>
+        <v>574</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1206</v>
+        <v>464</v>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -1271,13 +1287,13 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>114.54</v>
+        <v>651.5599999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>35.62</v>
+        <v>53.85</v>
       </c>
       <c r="U10" t="n">
-        <v>3.42</v>
+        <v>4.82</v>
       </c>
       <c r="V10" t="n">
         <v>237</v>
@@ -1305,25 +1321,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E11" t="n">
         <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="G11" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="H11" t="n">
-        <v>802</v>
+        <v>1862</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>502</v>
+        <v>1240</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -1354,13 +1370,13 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>143.32</v>
+        <v>129.2</v>
       </c>
       <c r="T11" t="n">
-        <v>49.06</v>
+        <v>38.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.79</v>
+        <v>3.32</v>
       </c>
       <c r="V11" t="n">
         <v>237</v>
@@ -1392,25 +1408,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
         <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G12" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H12" t="n">
-        <v>630</v>
+        <v>277</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>497</v>
+        <v>220</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -1441,13 +1457,13 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>630.96</v>
+        <v>675.8099999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>53.55</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>4.83</v>
+        <v>2.99</v>
       </c>
       <c r="V12" t="n">
         <v>237</v>
@@ -1479,33 +1495,37 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E13" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G13" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H13" t="n">
-        <v>3648</v>
+        <v>1107</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2367</v>
+        <v>883</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N13" t="n">
         <v>256</v>
       </c>
@@ -1524,19 +1544,23 @@
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>77.95999999999999</v>
+        <v>439.72</v>
       </c>
       <c r="T13" t="n">
-        <v>17.44</v>
+        <v>37.6</v>
       </c>
       <c r="U13" t="n">
-        <v>5.96</v>
+        <v>8.91</v>
       </c>
       <c r="V13" t="n">
         <v>237</v>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3</v>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -1558,33 +1582,37 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
         <v>200</v>
       </c>
       <c r="F14" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G14" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H14" t="n">
-        <v>453</v>
+        <v>1138</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>374</v>
+        <v>877</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N14" t="n">
         <v>256</v>
       </c>
@@ -1603,19 +1631,23 @@
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>480.14</v>
+        <v>308.18</v>
       </c>
       <c r="T14" t="n">
-        <v>73.04000000000001</v>
+        <v>35.12</v>
       </c>
       <c r="U14" t="n">
-        <v>5.13</v>
+        <v>9.51</v>
       </c>
       <c r="V14" t="n">
         <v>237</v>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3</v>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -1640,30 +1672,34 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F15" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G15" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H15" t="n">
-        <v>3405</v>
+        <v>6694</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2125</v>
+        <v>4346</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N15" t="n">
         <v>256</v>
       </c>
@@ -1682,19 +1718,23 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>95.01000000000001</v>
+        <v>111.51</v>
       </c>
       <c r="T15" t="n">
-        <v>17.15</v>
+        <v>26.42</v>
       </c>
       <c r="U15" t="n">
-        <v>6.02</v>
+        <v>14.63</v>
       </c>
       <c r="V15" t="n">
         <v>237</v>
       </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3</v>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -1716,37 +1756,33 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
         <v>50</v>
       </c>
-      <c r="E16" t="n">
-        <v>200</v>
-      </c>
       <c r="F16" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G16" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H16" t="n">
-        <v>488</v>
+        <v>295</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>378</v>
+        <v>235</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>256</v>
       </c>
@@ -1765,23 +1801,19 @@
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>415.33</v>
+        <v>629.77</v>
       </c>
       <c r="T16" t="n">
-        <v>76.92</v>
+        <v>77.66</v>
       </c>
       <c r="U16" t="n">
-        <v>5.15</v>
+        <v>2.97</v>
       </c>
       <c r="V16" t="n">
         <v>237</v>
       </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3</v>
-      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -1806,22 +1838,22 @@
         <v>100</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F17" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="G17" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="H17" t="n">
-        <v>1853</v>
+        <v>6654</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1206</v>
+        <v>4148</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1848,13 +1880,13 @@
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>163.47</v>
+        <v>87.38</v>
       </c>
       <c r="T17" t="n">
-        <v>42.47</v>
+        <v>17.48</v>
       </c>
       <c r="U17" t="n">
-        <v>3.42</v>
+        <v>14.65</v>
       </c>
       <c r="V17" t="n">
         <v>237</v>
@@ -1894,25 +1926,21 @@
         <v>5000</v>
       </c>
       <c r="H18" t="n">
-        <v>272</v>
+        <v>1762</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>203</v>
+        <v>1098</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
         <v>256</v>
       </c>
@@ -1931,23 +1959,19 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>661.87</v>
+        <v>262.85</v>
       </c>
       <c r="T18" t="n">
-        <v>76.18000000000001</v>
+        <v>62.03</v>
       </c>
       <c r="U18" t="n">
-        <v>2.94</v>
+        <v>3.41</v>
       </c>
       <c r="V18" t="n">
         <v>237</v>
       </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3</v>
-      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -1969,25 +1993,25 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" t="n">
         <v>100</v>
       </c>
-      <c r="E19" t="n">
-        <v>200</v>
-      </c>
       <c r="F19" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="G19" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="H19" t="n">
-        <v>6144</v>
+        <v>1580</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3864</v>
+        <v>952</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -2018,13 +2042,13 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>169.08</v>
+        <v>119.1</v>
       </c>
       <c r="T19" t="n">
-        <v>36.64</v>
+        <v>40.37</v>
       </c>
       <c r="U19" t="n">
-        <v>13.64</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>237</v>
@@ -2059,34 +2083,30 @@
         <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G20" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>1804</v>
+        <v>3288</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1137</v>
+        <v>1989</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
         <v>256</v>
       </c>
@@ -2105,23 +2125,19 @@
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>134.5</v>
+        <v>136.8</v>
       </c>
       <c r="T20" t="n">
-        <v>39.9</v>
+        <v>28.02</v>
       </c>
       <c r="U20" t="n">
-        <v>3.26</v>
+        <v>5.57</v>
       </c>
       <c r="V20" t="n">
         <v>237</v>
       </c>
-      <c r="W20" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3</v>
-      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -2143,25 +2159,25 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E21" t="n">
         <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="G21" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>799</v>
+        <v>3394</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>508</v>
+        <v>2149</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -2192,13 +2208,13 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>171.48</v>
+        <v>150.96</v>
       </c>
       <c r="T21" t="n">
-        <v>60.06</v>
+        <v>27.31</v>
       </c>
       <c r="U21" t="n">
-        <v>1.77</v>
+        <v>5.5</v>
       </c>
       <c r="V21" t="n">
         <v>237</v>
@@ -2242,25 +2258,21 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>3111</v>
+        <v>487</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1865</v>
+        <v>397</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>256</v>
       </c>
@@ -2279,23 +2291,19 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>98.72</v>
+        <v>543.72</v>
       </c>
       <c r="T22" t="n">
-        <v>23.49</v>
+        <v>68.86</v>
       </c>
       <c r="U22" t="n">
-        <v>6.39</v>
+        <v>4.85</v>
       </c>
       <c r="V22" t="n">
         <v>237</v>
       </c>
-      <c r="W22" t="n">
-        <v>1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3</v>
-      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -2317,33 +2325,37 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>50</v>
+      </c>
+      <c r="E23" t="n">
         <v>100</v>
       </c>
-      <c r="E23" t="n">
-        <v>200</v>
-      </c>
       <c r="F23" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="G23" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="H23" t="n">
-        <v>6945</v>
+        <v>237</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>4475</v>
+        <v>177</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N23" t="n">
         <v>256</v>
       </c>
@@ -2362,19 +2374,23 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>108.38</v>
+        <v>610.33</v>
       </c>
       <c r="T23" t="n">
-        <v>22.84</v>
+        <v>88.16</v>
       </c>
       <c r="U23" t="n">
-        <v>12.95</v>
+        <v>2.82</v>
       </c>
       <c r="V23" t="n">
         <v>237</v>
       </c>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3</v>
+      </c>
       <c r="Y23" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -2396,10 +2412,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F24" t="n">
         <v>10000</v>
@@ -2408,13 +2424,13 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>536</v>
+        <v>433</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>407</v>
+        <v>344</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -2445,13 +2461,13 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>470.35</v>
+        <v>442.55</v>
       </c>
       <c r="T24" t="n">
-        <v>56.24</v>
+        <v>74.81</v>
       </c>
       <c r="U24" t="n">
-        <v>5.18</v>
+        <v>5.12</v>
       </c>
       <c r="V24" t="n">
         <v>237</v>
@@ -2483,28 +2499,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E25" t="n">
         <v>50</v>
       </c>
       <c r="F25" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="G25" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>159</v>
+        <v>3732</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>130</v>
+        <v>2460</v>
       </c>
       <c r="K25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -2528,13 +2544,13 @@
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>573.08</v>
+        <v>202.06</v>
       </c>
       <c r="T25" t="n">
-        <v>101.18</v>
+        <v>37.58</v>
       </c>
       <c r="U25" t="n">
-        <v>1.81</v>
+        <v>5.61</v>
       </c>
       <c r="V25" t="n">
         <v>237</v>
@@ -2574,25 +2590,21 @@
         <v>5000</v>
       </c>
       <c r="H26" t="n">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
         <v>256</v>
       </c>
@@ -2611,23 +2623,19 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>520.5599999999999</v>
+        <v>443.72</v>
       </c>
       <c r="T26" t="n">
-        <v>101.18</v>
+        <v>82.78</v>
       </c>
       <c r="U26" t="n">
-        <v>2.8</v>
+        <v>3.57</v>
       </c>
       <c r="V26" t="n">
         <v>237</v>
       </c>
-      <c r="W26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3</v>
-      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -2649,10 +2657,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" t="n">
         <v>200</v>
-      </c>
-      <c r="E27" t="n">
-        <v>50</v>
       </c>
       <c r="F27" t="n">
         <v>10000</v>
@@ -2661,25 +2669,21 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>3414</v>
+        <v>536</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2172</v>
+        <v>434</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="b">
-        <v>1</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
         <v>256</v>
       </c>
@@ -2698,23 +2702,19 @@
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>177.4</v>
+        <v>361.91</v>
       </c>
       <c r="T27" t="n">
-        <v>31.05</v>
+        <v>65.89</v>
       </c>
       <c r="U27" t="n">
-        <v>5.51</v>
+        <v>5.2</v>
       </c>
       <c r="V27" t="n">
         <v>237</v>
       </c>
-      <c r="W27" t="n">
-        <v>1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3</v>
-      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -2736,28 +2736,28 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E28" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="G28" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>149</v>
+        <v>3390</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>119</v>
+        <v>2279</v>
       </c>
       <c r="K28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
@@ -2785,13 +2785,13 @@
         <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>666.88</v>
+        <v>116.55</v>
       </c>
       <c r="T28" t="n">
-        <v>112.6</v>
+        <v>27.26</v>
       </c>
       <c r="U28" t="n">
-        <v>1.78</v>
+        <v>6.54</v>
       </c>
       <c r="V28" t="n">
         <v>237</v>
@@ -2823,33 +2823,37 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>2500</v>
+        <v>20000</v>
       </c>
       <c r="G29" t="n">
-        <v>2500</v>
+        <v>20000</v>
       </c>
       <c r="H29" t="n">
-        <v>951</v>
+        <v>6349</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>623</v>
+        <v>3464</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N29" t="n">
         <v>256</v>
       </c>
@@ -2868,19 +2872,23 @@
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>105.16</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="T29" t="n">
-        <v>35.17</v>
+        <v>16.21</v>
       </c>
       <c r="U29" t="n">
-        <v>1.81</v>
+        <v>13.12</v>
       </c>
       <c r="V29" t="n">
         <v>237</v>
       </c>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3</v>
+      </c>
       <c r="Y29" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -2902,10 +2910,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" t="n">
         <v>200</v>
-      </c>
-      <c r="E30" t="n">
-        <v>50</v>
       </c>
       <c r="F30" t="n">
         <v>10000</v>
@@ -2914,16 +2922,16 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>490</v>
+        <v>3439</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>393</v>
+        <v>2234</v>
       </c>
       <c r="K30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -2947,13 +2955,13 @@
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>628.12</v>
+        <v>103.92</v>
       </c>
       <c r="T30" t="n">
-        <v>52.99</v>
+        <v>31.71</v>
       </c>
       <c r="U30" t="n">
-        <v>4.85</v>
+        <v>6.01</v>
       </c>
       <c r="V30" t="n">
         <v>237</v>
@@ -2984,30 +2992,34 @@
         <v>200</v>
       </c>
       <c r="E31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G31" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H31" t="n">
-        <v>3687</v>
+        <v>6736</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>2326</v>
+        <v>3707</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="b">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N31" t="n">
         <v>256</v>
       </c>
@@ -3026,19 +3038,23 @@
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>188.95</v>
+        <v>76.92</v>
       </c>
       <c r="T31" t="n">
-        <v>36.35</v>
+        <v>17.85</v>
       </c>
       <c r="U31" t="n">
-        <v>5.63</v>
+        <v>12.89</v>
       </c>
       <c r="V31" t="n">
         <v>237</v>
       </c>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3</v>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -3060,10 +3076,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
+        <v>200</v>
+      </c>
+      <c r="E32" t="n">
         <v>100</v>
-      </c>
-      <c r="E32" t="n">
-        <v>200</v>
       </c>
       <c r="F32" t="n">
         <v>20000</v>
@@ -3072,13 +3088,13 @@
         <v>20000</v>
       </c>
       <c r="H32" t="n">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>877</v>
+        <v>919</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -3109,13 +3125,13 @@
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>308.18</v>
+        <v>434.63</v>
       </c>
       <c r="T32" t="n">
-        <v>35.12</v>
+        <v>39.13</v>
       </c>
       <c r="U32" t="n">
-        <v>9.51</v>
+        <v>8.98</v>
       </c>
       <c r="V32" t="n">
         <v>237</v>
@@ -3150,22 +3166,22 @@
         <v>50</v>
       </c>
       <c r="E33" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F33" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="G33" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="H33" t="n">
-        <v>3439</v>
+        <v>951</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>2234</v>
+        <v>623</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
@@ -3192,13 +3208,13 @@
         <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>103.92</v>
+        <v>105.16</v>
       </c>
       <c r="T33" t="n">
-        <v>31.71</v>
+        <v>35.17</v>
       </c>
       <c r="U33" t="n">
-        <v>6.01</v>
+        <v>1.81</v>
       </c>
       <c r="V33" t="n">
         <v>237</v>
@@ -3229,22 +3245,22 @@
         <v>50</v>
       </c>
       <c r="E34" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F34" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G34" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>1453</v>
+        <v>3117</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>965</v>
+        <v>1841</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
@@ -3275,13 +3291,13 @@
         <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>193.99</v>
+        <v>105.69</v>
       </c>
       <c r="T34" t="n">
-        <v>60.13</v>
+        <v>37</v>
       </c>
       <c r="U34" t="n">
-        <v>3.01</v>
+        <v>5.71</v>
       </c>
       <c r="V34" t="n">
         <v>237</v>
@@ -3313,25 +3329,25 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E35" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F35" t="n">
-        <v>20000</v>
+        <v>2500</v>
       </c>
       <c r="G35" t="n">
-        <v>20000</v>
+        <v>2500</v>
       </c>
       <c r="H35" t="n">
-        <v>930</v>
+        <v>152</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>735</v>
+        <v>125</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -3358,13 +3374,13 @@
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>463.41</v>
+        <v>592.8200000000001</v>
       </c>
       <c r="T35" t="n">
-        <v>52.13</v>
+        <v>100.66</v>
       </c>
       <c r="U35" t="n">
-        <v>8.949999999999999</v>
+        <v>1.77</v>
       </c>
       <c r="V35" t="n">
         <v>237</v>
@@ -3395,22 +3411,22 @@
         <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F36" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G36" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H36" t="n">
-        <v>585</v>
+        <v>950</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>476</v>
+        <v>704</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -3441,13 +3457,13 @@
         <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>471.41</v>
+        <v>360.81</v>
       </c>
       <c r="T36" t="n">
-        <v>59.66</v>
+        <v>30.94</v>
       </c>
       <c r="U36" t="n">
-        <v>6.05</v>
+        <v>11.69</v>
       </c>
       <c r="V36" t="n">
         <v>237</v>
@@ -3479,10 +3495,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" t="n">
         <v>50</v>
-      </c>
-      <c r="E37" t="n">
-        <v>100</v>
       </c>
       <c r="F37" t="n">
         <v>5000</v>
@@ -3491,16 +3507,16 @@
         <v>5000</v>
       </c>
       <c r="H37" t="n">
-        <v>1932</v>
+        <v>267</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1352</v>
+        <v>222</v>
       </c>
       <c r="K37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -3524,13 +3540,13 @@
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>112.28</v>
+        <v>590.0700000000001</v>
       </c>
       <c r="T37" t="n">
-        <v>42.86</v>
+        <v>68.59</v>
       </c>
       <c r="U37" t="n">
-        <v>3.86</v>
+        <v>3.12</v>
       </c>
       <c r="V37" t="n">
         <v>237</v>
@@ -3558,37 +3574,33 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E38" t="n">
         <v>50</v>
       </c>
       <c r="F38" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="G38" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="H38" t="n">
-        <v>578</v>
+        <v>952</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>452</v>
+        <v>604</v>
       </c>
       <c r="K38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="b">
-        <v>1</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
         <v>256</v>
       </c>
@@ -3607,23 +3619,19 @@
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>622.45</v>
+        <v>121.82</v>
       </c>
       <c r="T38" t="n">
-        <v>52.46</v>
+        <v>46.42</v>
       </c>
       <c r="U38" t="n">
-        <v>4.87</v>
+        <v>1.81</v>
       </c>
       <c r="V38" t="n">
         <v>237</v>
       </c>
-      <c r="W38" t="n">
-        <v>1</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3</v>
-      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -3645,37 +3653,33 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E39" t="n">
         <v>200</v>
       </c>
       <c r="F39" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G39" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H39" t="n">
-        <v>3453</v>
+        <v>969</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>2258</v>
+        <v>775</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="b">
-        <v>1</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
         <v>256</v>
       </c>
@@ -3694,23 +3698,19 @@
         <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>128.36</v>
+        <v>392.56</v>
       </c>
       <c r="T39" t="n">
-        <v>51.37</v>
+        <v>48.76</v>
       </c>
       <c r="U39" t="n">
-        <v>5.83</v>
+        <v>12.04</v>
       </c>
       <c r="V39" t="n">
         <v>237</v>
       </c>
-      <c r="W39" t="n">
-        <v>1</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3</v>
-      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -3744,16 +3744,16 @@
         <v>5000</v>
       </c>
       <c r="H40" t="n">
-        <v>239</v>
+        <v>1795</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>198</v>
+        <v>1206</v>
       </c>
       <c r="K40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -3777,13 +3777,13 @@
         <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>626.4</v>
+        <v>114.54</v>
       </c>
       <c r="T40" t="n">
-        <v>116.4</v>
+        <v>35.62</v>
       </c>
       <c r="U40" t="n">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="V40" t="n">
         <v>237</v>
@@ -3811,33 +3811,37 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E41" t="n">
         <v>50</v>
       </c>
       <c r="F41" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="G41" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="H41" t="n">
-        <v>574</v>
+        <v>802</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>464</v>
+        <v>502</v>
       </c>
       <c r="K41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="b">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N41" t="n">
         <v>256</v>
       </c>
@@ -3856,19 +3860,23 @@
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>651.5599999999999</v>
+        <v>143.32</v>
       </c>
       <c r="T41" t="n">
-        <v>53.85</v>
+        <v>49.06</v>
       </c>
       <c r="U41" t="n">
-        <v>4.82</v>
+        <v>1.79</v>
       </c>
       <c r="V41" t="n">
         <v>237</v>
       </c>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3</v>
+      </c>
       <c r="Y41" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -3890,28 +3898,28 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E42" t="n">
         <v>50</v>
       </c>
       <c r="F42" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G42" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>1862</v>
+        <v>630</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1240</v>
+        <v>497</v>
       </c>
       <c r="K42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="b">
         <v>1</v>
@@ -3939,13 +3947,13 @@
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>129.2</v>
+        <v>630.96</v>
       </c>
       <c r="T42" t="n">
-        <v>38.98</v>
+        <v>53.55</v>
       </c>
       <c r="U42" t="n">
-        <v>3.32</v>
+        <v>4.83</v>
       </c>
       <c r="V42" t="n">
         <v>237</v>
@@ -3977,37 +3985,33 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E43" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F43" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G43" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>277</v>
+        <v>3648</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>220</v>
+        <v>2367</v>
       </c>
       <c r="K43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>256</v>
       </c>
@@ -4026,23 +4030,19 @@
         <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>675.8099999999999</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="T43" t="n">
-        <v>78.56999999999999</v>
+        <v>17.44</v>
       </c>
       <c r="U43" t="n">
-        <v>2.99</v>
+        <v>5.96</v>
       </c>
       <c r="V43" t="n">
         <v>237</v>
       </c>
-      <c r="W43" t="n">
-        <v>1</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3</v>
-      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -4064,37 +4064,33 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
+        <v>50</v>
+      </c>
+      <c r="E44" t="n">
         <v>200</v>
       </c>
-      <c r="E44" t="n">
-        <v>100</v>
-      </c>
       <c r="F44" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="G44" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>1107</v>
+        <v>453</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>883</v>
+        <v>374</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
       </c>
       <c r="L44" t="b">
-        <v>1</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
         <v>256</v>
       </c>
@@ -4113,23 +4109,19 @@
         <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>439.72</v>
+        <v>480.14</v>
       </c>
       <c r="T44" t="n">
-        <v>37.6</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="U44" t="n">
-        <v>8.91</v>
+        <v>5.13</v>
       </c>
       <c r="V44" t="n">
         <v>237</v>
       </c>
-      <c r="W44" t="n">
-        <v>1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3</v>
-      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -4151,37 +4143,33 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E45" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F45" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="G45" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>6694</v>
+        <v>490</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>4346</v>
+        <v>393</v>
       </c>
       <c r="K45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
         <v>256</v>
       </c>
@@ -4200,23 +4188,19 @@
         <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>111.51</v>
+        <v>628.12</v>
       </c>
       <c r="T45" t="n">
-        <v>26.42</v>
+        <v>52.99</v>
       </c>
       <c r="U45" t="n">
-        <v>14.63</v>
+        <v>4.85</v>
       </c>
       <c r="V45" t="n">
         <v>237</v>
       </c>
-      <c r="W45" t="n">
-        <v>1</v>
-      </c>
-      <c r="X45" t="n">
-        <v>3</v>
-      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -4250,25 +4234,21 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>3390</v>
+        <v>534</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>2279</v>
+        <v>426</v>
       </c>
       <c r="K46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
         <v>256</v>
       </c>
@@ -4287,23 +4267,19 @@
         <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>116.55</v>
+        <v>484.09</v>
       </c>
       <c r="T46" t="n">
-        <v>27.26</v>
+        <v>61.23</v>
       </c>
       <c r="U46" t="n">
-        <v>6.54</v>
+        <v>4.84</v>
       </c>
       <c r="V46" t="n">
         <v>237</v>
       </c>
-      <c r="W46" t="n">
-        <v>1</v>
-      </c>
-      <c r="X46" t="n">
-        <v>3</v>
-      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -4328,25 +4304,25 @@
         <v>100</v>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F47" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G47" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>295</v>
+        <v>3405</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>235</v>
+        <v>2125</v>
       </c>
       <c r="K47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -4370,13 +4346,13 @@
         <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>629.77</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="T47" t="n">
-        <v>77.66</v>
+        <v>17.15</v>
       </c>
       <c r="U47" t="n">
-        <v>2.97</v>
+        <v>6.02</v>
       </c>
       <c r="V47" t="n">
         <v>237</v>
@@ -4407,30 +4383,34 @@
         <v>100</v>
       </c>
       <c r="E48" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F48" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="G48" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="H48" t="n">
-        <v>6654</v>
+        <v>272</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>4148</v>
+        <v>203</v>
       </c>
       <c r="K48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="b">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N48" t="n">
         <v>256</v>
       </c>
@@ -4449,19 +4429,23 @@
         <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>87.38</v>
+        <v>661.87</v>
       </c>
       <c r="T48" t="n">
-        <v>17.48</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="U48" t="n">
-        <v>14.65</v>
+        <v>2.94</v>
       </c>
       <c r="V48" t="n">
         <v>237</v>
       </c>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3</v>
+      </c>
       <c r="Y48" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -4486,30 +4470,34 @@
         <v>100</v>
       </c>
       <c r="E49" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F49" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="G49" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="H49" t="n">
-        <v>1762</v>
+        <v>6144</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1098</v>
+        <v>3864</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="b">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N49" t="n">
         <v>256</v>
       </c>
@@ -4528,19 +4516,23 @@
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>262.85</v>
+        <v>169.08</v>
       </c>
       <c r="T49" t="n">
-        <v>62.03</v>
+        <v>36.64</v>
       </c>
       <c r="U49" t="n">
-        <v>3.41</v>
+        <v>13.64</v>
       </c>
       <c r="V49" t="n">
         <v>237</v>
       </c>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
+      <c r="W49" t="n">
+        <v>1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3</v>
+      </c>
       <c r="Y49" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -4562,10 +4554,10 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" t="n">
         <v>50</v>
-      </c>
-      <c r="E50" t="n">
-        <v>100</v>
       </c>
       <c r="F50" t="n">
         <v>5000</v>
@@ -4574,13 +4566,13 @@
         <v>5000</v>
       </c>
       <c r="H50" t="n">
-        <v>1580</v>
+        <v>1804</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>952</v>
+        <v>1137</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
@@ -4611,13 +4603,13 @@
         <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>119.1</v>
+        <v>134.5</v>
       </c>
       <c r="T50" t="n">
-        <v>40.37</v>
+        <v>39.9</v>
       </c>
       <c r="U50" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="V50" t="n">
         <v>237</v>
@@ -4649,33 +4641,37 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E51" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="G51" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="H51" t="n">
-        <v>3288</v>
+        <v>799</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1989</v>
+        <v>508</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="b">
-        <v>0</v>
-      </c>
-      <c r="M51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N51" t="n">
         <v>256</v>
       </c>
@@ -4694,19 +4690,23 @@
         <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>136.8</v>
+        <v>171.48</v>
       </c>
       <c r="T51" t="n">
-        <v>28.02</v>
+        <v>60.06</v>
       </c>
       <c r="U51" t="n">
-        <v>5.57</v>
+        <v>1.77</v>
       </c>
       <c r="V51" t="n">
         <v>237</v>
       </c>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>3</v>
+      </c>
       <c r="Y51" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -4728,10 +4728,10 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F52" t="n">
         <v>10000</v>
@@ -4740,13 +4740,13 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3394</v>
+        <v>3111</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>2149</v>
+        <v>1865</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
@@ -4777,13 +4777,13 @@
         <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>150.96</v>
+        <v>98.72</v>
       </c>
       <c r="T52" t="n">
-        <v>27.31</v>
+        <v>23.49</v>
       </c>
       <c r="U52" t="n">
-        <v>5.5</v>
+        <v>6.39</v>
       </c>
       <c r="V52" t="n">
         <v>237</v>
@@ -4818,25 +4818,25 @@
         <v>100</v>
       </c>
       <c r="E53" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F53" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G53" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H53" t="n">
-        <v>487</v>
+        <v>6945</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>397</v>
+        <v>4475</v>
       </c>
       <c r="K53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -4860,13 +4860,13 @@
         <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>543.72</v>
+        <v>108.38</v>
       </c>
       <c r="T53" t="n">
-        <v>68.86</v>
+        <v>22.84</v>
       </c>
       <c r="U53" t="n">
-        <v>4.85</v>
+        <v>12.95</v>
       </c>
       <c r="V53" t="n">
         <v>237</v>
@@ -4894,25 +4894,25 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E54" t="n">
         <v>100</v>
       </c>
       <c r="F54" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G54" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>237</v>
+        <v>536</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>177</v>
+        <v>407</v>
       </c>
       <c r="K54" t="b">
         <v>0</v>
@@ -4943,13 +4943,13 @@
         <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>610.33</v>
+        <v>470.35</v>
       </c>
       <c r="T54" t="n">
-        <v>88.16</v>
+        <v>56.24</v>
       </c>
       <c r="U54" t="n">
-        <v>2.82</v>
+        <v>5.18</v>
       </c>
       <c r="V54" t="n">
         <v>237</v>
@@ -4984,34 +4984,30 @@
         <v>50</v>
       </c>
       <c r="E55" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="G55" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="H55" t="n">
-        <v>433</v>
+        <v>159</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>344</v>
+        <v>130</v>
       </c>
       <c r="K55" t="b">
         <v>0</v>
       </c>
       <c r="L55" t="b">
-        <v>1</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
         <v>256</v>
       </c>
@@ -5030,23 +5026,19 @@
         <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>442.55</v>
+        <v>573.08</v>
       </c>
       <c r="T55" t="n">
-        <v>74.81</v>
+        <v>101.18</v>
       </c>
       <c r="U55" t="n">
-        <v>5.12</v>
+        <v>1.81</v>
       </c>
       <c r="V55" t="n">
         <v>237</v>
       </c>
-      <c r="W55" t="n">
-        <v>1</v>
-      </c>
-      <c r="X55" t="n">
-        <v>3</v>
-      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -5068,33 +5060,37 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F56" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G56" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H56" t="n">
-        <v>3732</v>
+        <v>295</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>2460</v>
+        <v>224</v>
       </c>
       <c r="K56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="b">
-        <v>0</v>
-      </c>
-      <c r="M56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N56" t="n">
         <v>256</v>
       </c>
@@ -5113,19 +5109,23 @@
         <v>1</v>
       </c>
       <c r="S56" t="n">
-        <v>202.06</v>
+        <v>520.5599999999999</v>
       </c>
       <c r="T56" t="n">
-        <v>37.58</v>
+        <v>101.18</v>
       </c>
       <c r="U56" t="n">
-        <v>5.61</v>
+        <v>2.8</v>
       </c>
       <c r="V56" t="n">
         <v>237</v>
       </c>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
+      <c r="W56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X56" t="n">
+        <v>3</v>
+      </c>
       <c r="Y56" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -5147,33 +5147,37 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
+        <v>200</v>
+      </c>
+      <c r="E57" t="n">
         <v>50</v>
       </c>
-      <c r="E57" t="n">
-        <v>100</v>
-      </c>
       <c r="F57" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G57" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>312</v>
+        <v>3414</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>251</v>
+        <v>2172</v>
       </c>
       <c r="K57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="b">
-        <v>0</v>
-      </c>
-      <c r="M57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N57" t="n">
         <v>256</v>
       </c>
@@ -5192,19 +5196,23 @@
         <v>1</v>
       </c>
       <c r="S57" t="n">
-        <v>443.72</v>
+        <v>177.4</v>
       </c>
       <c r="T57" t="n">
-        <v>82.78</v>
+        <v>31.05</v>
       </c>
       <c r="U57" t="n">
-        <v>3.57</v>
+        <v>5.51</v>
       </c>
       <c r="V57" t="n">
         <v>237</v>
       </c>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
+      <c r="W57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X57" t="n">
+        <v>3</v>
+      </c>
       <c r="Y57" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -5229,30 +5237,34 @@
         <v>50</v>
       </c>
       <c r="E58" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="G58" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="H58" t="n">
-        <v>536</v>
+        <v>149</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>434</v>
+        <v>119</v>
       </c>
       <c r="K58" t="b">
         <v>0</v>
       </c>
       <c r="L58" t="b">
-        <v>0</v>
-      </c>
-      <c r="M58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="N58" t="n">
         <v>256</v>
       </c>
@@ -5271,19 +5283,23 @@
         <v>1</v>
       </c>
       <c r="S58" t="n">
-        <v>361.91</v>
+        <v>666.88</v>
       </c>
       <c r="T58" t="n">
-        <v>65.89</v>
+        <v>112.6</v>
       </c>
       <c r="U58" t="n">
-        <v>5.2</v>
+        <v>1.78</v>
       </c>
       <c r="V58" t="n">
         <v>237</v>
       </c>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
+      <c r="W58" t="n">
+        <v>1</v>
+      </c>
+      <c r="X58" t="n">
+        <v>3</v>
+      </c>
       <c r="Y58" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
@@ -5305,25 +5321,25 @@
         <v>1</v>
       </c>
       <c r="D59" t="n">
+        <v>50</v>
+      </c>
+      <c r="E59" t="n">
         <v>200</v>
       </c>
-      <c r="E59" t="n">
-        <v>100</v>
-      </c>
       <c r="F59" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="G59" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>1144</v>
+        <v>488</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>919</v>
+        <v>378</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -5354,13 +5370,13 @@
         <v>1</v>
       </c>
       <c r="S59" t="n">
-        <v>434.63</v>
+        <v>415.33</v>
       </c>
       <c r="T59" t="n">
-        <v>39.13</v>
+        <v>76.92</v>
       </c>
       <c r="U59" t="n">
-        <v>8.98</v>
+        <v>5.15</v>
       </c>
       <c r="V59" t="n">
         <v>237</v>
@@ -5372,6 +5388,247 @@
         <v>3</v>
       </c>
       <c r="Y59" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C60" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>100</v>
+      </c>
+      <c r="E60" t="n">
+        <v>50</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1853</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1206</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>256</v>
+      </c>
+      <c r="O60" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R60" t="b">
+        <v>1</v>
+      </c>
+      <c r="S60" t="n">
+        <v>163.47</v>
+      </c>
+      <c r="T60" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V60" t="n">
+        <v>237</v>
+      </c>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C61" t="b">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>200</v>
+      </c>
+      <c r="E61" t="n">
+        <v>50</v>
+      </c>
+      <c r="F61" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G61" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3687</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2326</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>256</v>
+      </c>
+      <c r="O61" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R61" t="b">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
+        <v>188.95</v>
+      </c>
+      <c r="T61" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="U61" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="V61" t="n">
+        <v>237</v>
+      </c>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C62" t="b">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>200</v>
+      </c>
+      <c r="E62" t="n">
+        <v>100</v>
+      </c>
+      <c r="F62" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H62" t="n">
+        <v>960</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>727</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>256</v>
+      </c>
+      <c r="O62" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R62" t="b">
+        <v>1</v>
+      </c>
+      <c r="S62" t="n">
+        <v>396.94</v>
+      </c>
+      <c r="T62" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="U62" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="V62" t="n">
+        <v>237</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
